--- a/exports/treasury/treasury_curveTradesRecap_skew.xlsx
+++ b/exports/treasury/treasury_curveTradesRecap_skew.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccardo/Desktop/Personal Projects/Latest/Yield curve models/gauss+/exports/treasury/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BC61D3-6E7B-1245-9134-253E6715E43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D509E30-D08A-D345-944D-2733BD94F45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="680" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <t>Source: BSIC</t>
   </si>
   <si>
-    <t>U.S. Treasuries, Skew</t>
+    <t>U.S. Treasuries, average skew</t>
   </si>
 </sst>
 </file>
@@ -504,8 +504,8 @@
   <dimension ref="B2:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="6" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
